--- a/data/trans_camb/P23_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 7,68</t>
+          <t>-4,75; 8,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 0,12</t>
+          <t>-12,52; -0,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -9,1</t>
+          <t>-19,78; -8,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,3</t>
+          <t>-5,76; 9,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,5; -2,07</t>
+          <t>-15,78; -2,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,36; -6,39</t>
+          <t>-18,67; -6,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 6,42</t>
+          <t>-3,47; 6,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -2,75</t>
+          <t>-12,2; -3,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -9,84</t>
+          <t>-17,67; -9,77</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 27,89</t>
+          <t>-14,16; 29,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,28; -1,14</t>
+          <t>-36,89; 0,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,26; -31,31</t>
+          <t>-58,36; -29,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 38,27</t>
+          <t>-17,46; 38,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,64; -8,0</t>
+          <t>-48,94; -9,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,49; -27,08</t>
+          <t>-57,8; -28,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 23,43</t>
+          <t>-10,71; 22,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,82; -10,02</t>
+          <t>-38,33; -11,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,1; -34,82</t>
+          <t>-54,68; -34,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 7,26</t>
+          <t>-6,85; 6,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 0,48</t>
+          <t>-12,92; 0,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -7,47</t>
+          <t>-21,0; -7,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 9,29</t>
+          <t>-6,37; 8,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -0,99</t>
+          <t>-15,66; -1,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,58; -6,84</t>
+          <t>-19,62; -6,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 6,21</t>
+          <t>-4,57; 5,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,55; -2,46</t>
+          <t>-12,11; -2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -9,42</t>
+          <t>-18,4; -9,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 23,99</t>
+          <t>-17,92; 21,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 1,51</t>
+          <t>-34,37; 1,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,76; -24,18</t>
+          <t>-53,94; -24,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 28,75</t>
+          <t>-16,36; 27,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,16; -2,19</t>
+          <t>-39,74; -2,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,53; -21,79</t>
+          <t>-50,99; -22,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 19,23</t>
+          <t>-12,07; 18,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,75; -7,54</t>
+          <t>-32,97; -7,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,84; -29,35</t>
+          <t>-49,36; -28,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 0,39</t>
+          <t>-11,15; 1,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 2,49</t>
+          <t>-9,82; 2,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,22; -15,3</t>
+          <t>-39,67; -14,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 14,6</t>
+          <t>-3,15; 14,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 15,01</t>
+          <t>-4,32; 16,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -1,97</t>
+          <t>-19,48; -3,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 2,02</t>
+          <t>-8,32; 1,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 3,45</t>
+          <t>-7,1; 3,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-36,4; -15,0</t>
+          <t>-34,36; -14,6</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 0,9</t>
+          <t>-22,99; 2,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 6,02</t>
+          <t>-20,63; 6,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,33; -34,11</t>
+          <t>-83,47; -32,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 71,5</t>
+          <t>-10,14; 71,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 69,54</t>
+          <t>-14,85; 75,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,77; -9,38</t>
+          <t>-60,77; -14,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 5,46</t>
+          <t>-19,08; 5,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 9,05</t>
+          <t>-16,49; 9,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-82,99; -37,41</t>
+          <t>-78,08; -36,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 1,59</t>
+          <t>-6,5; 1,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,26; -1,38</t>
+          <t>-10,06; -1,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -5,67</t>
+          <t>-14,48; -5,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 9,88</t>
+          <t>-0,31; 10,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 11,4</t>
+          <t>1,65; 11,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,43; -2,91</t>
+          <t>-21,73; -2,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,44</t>
+          <t>-2,7; 3,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 2,05</t>
+          <t>-4,07; 2,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -7,25</t>
+          <t>-21,54; -6,96</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 3,74</t>
+          <t>-14,47; 3,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,03; -3,4</t>
+          <t>-22,25; -3,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,01; -13,51</t>
+          <t>-32,76; -13,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 33,53</t>
+          <t>-0,72; 34,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 39,23</t>
+          <t>4,78; 41,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,97; -9,54</t>
+          <t>-65,0; -8,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 9,13</t>
+          <t>-6,73; 10,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 5,46</t>
+          <t>-10,08; 5,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,86; -19,09</t>
+          <t>-56,01; -18,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -2,16</t>
+          <t>-16,14; -1,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,66; -2,97</t>
+          <t>-15,68; -2,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-21,99; -7,4</t>
+          <t>-21,57; -7,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 2,38</t>
+          <t>-7,2; 2,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 3,95</t>
+          <t>-6,58; 3,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -6,99</t>
+          <t>-17,64; -6,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,28; -0,55</t>
+          <t>-8,86; -0,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,34</t>
+          <t>-7,78; 0,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,7; -8,96</t>
+          <t>-18,32; -8,85</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,37; -4,8</t>
+          <t>-30,23; -3,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -6,56</t>
+          <t>-30,09; -5,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,23; -17,03</t>
+          <t>-41,6; -17,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 8,8</t>
+          <t>-21,37; 10,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 14,14</t>
+          <t>-19,67; 13,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,85; -24,59</t>
+          <t>-54,01; -23,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,7; -1,13</t>
+          <t>-22,14; -2,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 0,69</t>
+          <t>-19,45; 1,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,76; -25,45</t>
+          <t>-46,15; -25,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,66; -0,92</t>
+          <t>-14,35; -0,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 5,07</t>
+          <t>-8,94; 4,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,19; -5,14</t>
+          <t>-23,35; -4,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 3,88</t>
+          <t>-1,74; 3,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,64</t>
+          <t>-0,31; 5,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1,16</t>
+          <t>-4,79; 1,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,88</t>
+          <t>-3,26; 2,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,6</t>
+          <t>-0,77; 5,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -0,65</t>
+          <t>-7,41; -1,17</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,78; -3,41</t>
+          <t>-47,08; -0,99</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 21,82</t>
+          <t>-30,58; 19,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-75,71; -21,01</t>
+          <t>-79,24; -16,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 32,0</t>
+          <t>-11,68; 32,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 46,13</t>
+          <t>-2,61; 46,33</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 9,39</t>
+          <t>-33,25; 10,93</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 12,78</t>
+          <t>-19,09; 14,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 31,92</t>
+          <t>-4,51; 35,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-42,33; -4,73</t>
+          <t>-43,52; -7,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,29; -0,34</t>
+          <t>-5,33; -0,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -2,9</t>
+          <t>-7,68; -2,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-20,9; -12,32</t>
+          <t>-21,41; -12,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,84</t>
+          <t>0,44; 4,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,84</t>
+          <t>-0,57; 3,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,14; -4,59</t>
+          <t>-10,04; -4,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,48</t>
+          <t>-1,66; 1,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,19</t>
+          <t>-3,4; -0,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,03; -8,98</t>
+          <t>-14,19; -9,05</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -0,83</t>
+          <t>-13,1; -0,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,15; -7,42</t>
+          <t>-18,72; -6,78</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-52,49; -31,7</t>
+          <t>-55,09; -31,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,52; 20,64</t>
+          <t>1,54; 19,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 16,42</t>
+          <t>-2,29; 16,13</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,24; -19,26</t>
+          <t>-40,15; -19,01</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 4,72</t>
+          <t>-5,02; 5,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,53; -0,68</t>
+          <t>-10,34; -0,47</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-44,21; -28,63</t>
+          <t>-44,01; -28,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-14,32</t>
+          <t>-14,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,68</t>
+          <t>-13,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-13,78</t>
+          <t>-13,83</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 8,18</t>
+          <t>-4,69; 7,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,52; -0,24</t>
+          <t>-12,68; 0,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -8,6</t>
+          <t>-19,66; -8,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 9,43</t>
+          <t>-5,69; 9,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -2,63</t>
+          <t>-15,11; -2,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -6,96</t>
+          <t>-19,27; -7,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 6,15</t>
+          <t>-3,15; 6,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,2; -3,19</t>
+          <t>-12,04; -2,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -9,77</t>
+          <t>-17,78; -10,08</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-46,01%</t>
+          <t>-44,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-45,06%</t>
+          <t>-46,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-46,0%</t>
+          <t>-46,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 29,11</t>
+          <t>-13,99; 26,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 0,07</t>
+          <t>-36,61; 1,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,36; -29,93</t>
+          <t>-56,95; -30,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 38,5</t>
+          <t>-18,05; 38,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,94; -9,96</t>
+          <t>-47,85; -9,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,8; -28,03</t>
+          <t>-59,35; -31,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 22,04</t>
+          <t>-9,75; 22,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,33; -11,34</t>
+          <t>-37,71; -10,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,68; -34,87</t>
+          <t>-55,17; -36,61</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-14,19</t>
+          <t>-15,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,18</t>
+          <t>-13,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-13,74</t>
+          <t>-14,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,76</t>
+          <t>-7,77; 6,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 0,45</t>
+          <t>-13,95; 0,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,0; -7,88</t>
+          <t>-21,78; -9,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 8,51</t>
+          <t>-6,14; 9,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -1,16</t>
+          <t>-14,48; -1,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -6,97</t>
+          <t>-19,21; -7,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,87</t>
+          <t>-4,36; 5,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -2,47</t>
+          <t>-12,15; -2,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -9,24</t>
+          <t>-18,71; -9,4</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-40,91%</t>
+          <t>-43,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-37,67%</t>
+          <t>-37,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-39,44%</t>
+          <t>-40,68%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 21,56</t>
+          <t>-20,45; 22,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 1,6</t>
+          <t>-36,14; 1,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,94; -24,39</t>
+          <t>-55,77; -28,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 27,33</t>
+          <t>-15,97; 28,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,74; -2,87</t>
+          <t>-37,58; -2,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,99; -22,11</t>
+          <t>-49,34; -22,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 18,68</t>
+          <t>-11,82; 17,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,97; -7,75</t>
+          <t>-33,3; -7,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,36; -28,14</t>
+          <t>-49,8; -29,37</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-27,34</t>
+          <t>-18,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,98</t>
+          <t>-11,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-23,38</t>
+          <t>-17,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 1,03</t>
+          <t>-11,22; 0,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 2,7</t>
+          <t>-10,04; 2,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -14,88</t>
+          <t>-24,98; -12,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 14,84</t>
+          <t>-3,45; 13,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 16,16</t>
+          <t>-5,04; 16,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -3,08</t>
+          <t>-20,36; -3,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 1,9</t>
+          <t>-8,39; 1,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 3,69</t>
+          <t>-7,23; 3,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-34,36; -14,6</t>
+          <t>-22,29; -12,56</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-60,34%</t>
+          <t>-40,27%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,82%</t>
+          <t>-44,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-57,29%</t>
+          <t>-42,38%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 2,2</t>
+          <t>-23,28; 1,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 6,42</t>
+          <t>-20,5; 5,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,47; -32,82</t>
+          <t>-51,45; -29,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 71,65</t>
+          <t>-10,83; 62,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 75,04</t>
+          <t>-15,93; 75,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,77; -14,53</t>
+          <t>-62,6; -17,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 5,19</t>
+          <t>-18,72; 4,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 9,84</t>
+          <t>-16,69; 9,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,08; -36,23</t>
+          <t>-51,5; -32,34</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,14</t>
+          <t>-10,75</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,03</t>
+          <t>-5,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-11,39</t>
+          <t>-9,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 1,45</t>
+          <t>-6,96; 1,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -1,7</t>
+          <t>-9,45; -1,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -5,65</t>
+          <t>-15,24; -6,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 10,14</t>
+          <t>-0,15; 9,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 11,94</t>
+          <t>0,74; 10,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,73; -2,5</t>
+          <t>-9,01; -0,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,8</t>
+          <t>-3,23; 3,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 2,1</t>
+          <t>-3,79; 2,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,54; -6,96</t>
+          <t>-12,04; -5,79</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-23,66%</t>
+          <t>-25,08%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-31,4%</t>
+          <t>-15,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-29,31%</t>
+          <t>-23,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 3,55</t>
+          <t>-15,28; 3,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -3,94</t>
+          <t>-20,93; -4,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -13,9</t>
+          <t>-33,64; -15,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 34,6</t>
+          <t>-0,58; 32,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 41,34</t>
+          <t>2,18; 35,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,0; -8,1</t>
+          <t>-26,42; -0,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 10,2</t>
+          <t>-7,86; 8,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 5,76</t>
+          <t>-9,36; 5,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,01; -18,66</t>
+          <t>-29,94; -15,48</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-15,03</t>
+          <t>-16,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-11,7</t>
+          <t>-9,6</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-13,27</t>
+          <t>-11,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,14; -1,46</t>
+          <t>-16,16; -2,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,68; -2,41</t>
+          <t>-16,53; -3,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -7,76</t>
+          <t>-23,11; -9,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 2,98</t>
+          <t>-7,43; 2,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 3,69</t>
+          <t>-6,5; 3,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -6,7</t>
+          <t>-14,19; -5,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -0,78</t>
+          <t>-8,98; -0,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 0,4</t>
+          <t>-7,82; 0,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,32; -8,85</t>
+          <t>-15,82; -7,7</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-30,99%</t>
+          <t>-33,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-38,27%</t>
+          <t>-31,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-35,48%</t>
+          <t>-31,57%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,23; -3,18</t>
+          <t>-30,58; -4,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,09; -5,77</t>
+          <t>-31,12; -7,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,6; -17,13</t>
+          <t>-44,43; -20,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 10,93</t>
+          <t>-22,48; 10,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 13,39</t>
+          <t>-19,36; 12,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,01; -23,57</t>
+          <t>-42,52; -18,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,14; -2,19</t>
+          <t>-22,24; -1,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 1,42</t>
+          <t>-19,76; 0,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,15; -25,44</t>
+          <t>-39,63; -21,9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-15,01</t>
+          <t>-15,73</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-4,47</t>
+          <t>-5,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -0,39</t>
+          <t>-15,07; -0,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 4,82</t>
+          <t>-9,44; 4,83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-23,35; -4,55</t>
+          <t>-22,54; -7,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,82</t>
+          <t>-2,17; 3,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 5,62</t>
+          <t>-0,45; 5,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,34</t>
+          <t>-5,06; 0,74</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,13</t>
+          <t>-3,23; 2,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,17</t>
+          <t>-0,94; 4,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -1,17</t>
+          <t>-7,81; -1,83</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-55,29%</t>
+          <t>-57,92%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-15,07%</t>
+          <t>-18,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-27,97%</t>
+          <t>-31,29%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,08; -0,99</t>
+          <t>-49,86; -1,1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 19,17</t>
+          <t>-30,56; 20,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-79,24; -16,65</t>
+          <t>-76,55; -27,89</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 32,81</t>
+          <t>-14,18; 30,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 46,33</t>
+          <t>-3,07; 45,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 10,93</t>
+          <t>-34,83; 6,5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 14,85</t>
+          <t>-18,81; 14,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 35,63</t>
+          <t>-5,74; 32,26</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,52; -7,48</t>
+          <t>-45,45; -11,51</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-15,4</t>
+          <t>-13,93</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-6,72</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-11,03</t>
+          <t>-9,7</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -0,4</t>
+          <t>-5,3; -0,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,68; -2,63</t>
+          <t>-7,4; -2,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,41; -12,46</t>
+          <t>-16,43; -11,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,61</t>
+          <t>0,24; 4,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,74</t>
+          <t>-0,65; 3,71</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -4,43</t>
+          <t>-7,26; -3,55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,62</t>
+          <t>-1,83; 1,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,4; -0,15</t>
+          <t>-3,27; 0,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,19; -9,05</t>
+          <t>-11,25; -8,23</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-38,68%</t>
+          <t>-34,99%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-27,39%</t>
+          <t>-22,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-34,42%</t>
+          <t>-30,28%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -0,98</t>
+          <t>-12,93; -1,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -6,78</t>
+          <t>-18,29; -7,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,09; -31,88</t>
+          <t>-40,2; -29,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,54; 19,36</t>
+          <t>0,9; 19,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 16,13</t>
+          <t>-2,5; 15,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -19,01</t>
+          <t>-28,6; -15,24</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,17</t>
+          <t>-5,54; 4,55</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -0,47</t>
+          <t>-9,93; 0,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-44,01; -28,73</t>
+          <t>-34,19; -26,28</t>
         </is>
       </c>
     </row>
